--- a/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_SLB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_SLB.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Muhammad (16 L)</t>
+          <t>J. Slater (25 L)</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Muhammad (5.0 3PA)</t>
+          <t>J. Slater (9.0 3PA)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Slater (1.5)</t>
+          <t>L. Barrett (1.273)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Restricted Area (20 L)</t>
+          <t>Restricted Area (36 L)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Restricted Area (65.0%)</t>
+          <t>Restricted Area (77.8%)</t>
         </is>
       </c>
     </row>
@@ -545,15 +545,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -566,7 +566,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
@@ -574,7 +574,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -592,7 +592,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -930,134 +930,134 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>321694</t>
+          <t>321695</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>52.0%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>16</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>64.0%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>36.0%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
         <v>4</v>
       </c>
-      <c r="I2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>68.8%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
         <v>7</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>5</v>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
@@ -1065,41 +1065,41 @@
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="AN2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AT2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV2" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -1126,23 +1126,23 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>800.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
         <v>1</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG2" t="n">
@@ -1172,166 +1172,186 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>321695</t>
+          <t>321694</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>70.8%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
         <v>6</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
         <v>5</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
         <v>5</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AN3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
         <v>5</v>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AV3" t="n">
@@ -1339,18 +1359,18 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
         <v>2</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
@@ -1358,31 +1378,31 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -1418,138 +1438,158 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>59.1%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>64.7%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>77.3%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>3</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AN4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1561,18 +1601,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>200.0%</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
@@ -1580,31 +1620,747 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>272930</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>68.2%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>300.0%</t>
         </is>
       </c>
-      <c r="BC4" t="n">
+      <c r="AX5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>314018</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
         <v>4</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="AY6" t="n">
         <v>2</v>
       </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BG4" t="n">
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD6" t="n">
         <v>2</v>
       </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SLB_A._DZIEWA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>313937</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -1619,15 +2375,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -1640,7 +2396,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
@@ -1648,7 +2404,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -1666,7 +2422,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -2004,126 +2760,136 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>321695</t>
+          <t>321693</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>77.3%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>5</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AE2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
@@ -2133,60 +2899,60 @@
         </is>
       </c>
       <c r="AN2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
         <v>5</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2</v>
-      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -2197,7 +2963,7 @@
         <v>2</v>
       </c>
       <c r="BD2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -2214,7 +2980,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -2236,156 +3002,186 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>321693</t>
+          <t>272930</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" t="n">
+        <v>26</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>68.2%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
         <v>5</v>
       </c>
-      <c r="I3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>60.0%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>3</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="AV3" t="n">
@@ -2393,7 +3189,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
@@ -2412,23 +3208,23 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
@@ -2458,134 +3254,134 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>321694</t>
+          <t>321695</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>52.0%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>16</v>
       </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>64.0%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>36.0%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
         <v>4</v>
       </c>
-      <c r="I4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>68.8%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
         <v>7</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>5</v>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
@@ -2593,41 +3389,41 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="AN4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
@@ -2635,7 +3431,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
@@ -2654,23 +3450,23 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>800.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
         <v>1</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
@@ -2679,6 +3475,722 @@
       <c r="BH4" t="inlineStr">
         <is>
           <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>314018</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SLB_A._DZIEWA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>313937</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>321694</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>11</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>17</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>70.8%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>10</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -2693,15 +4205,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -2714,7 +4226,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
@@ -2722,7 +4234,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -2740,7 +4252,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -3078,134 +4590,134 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>321694</t>
+          <t>321695</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>52.0%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>16</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>64.0%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>36.0%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
         <v>4</v>
       </c>
-      <c r="I2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>68.8%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
         <v>7</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>5</v>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
@@ -3213,41 +4725,41 @@
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="AN2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AT2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV2" t="n">
@@ -3255,7 +4767,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -3274,23 +4786,23 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>800.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
         <v>1</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG2" t="n">
@@ -3320,178 +4832,198 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>321695</t>
+          <t>272930</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>68.2%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
         <v>6</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
         <v>2</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>5</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AV3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>1</v>
       </c>
       <c r="AY3" t="n">
         <v>2</v>
@@ -3502,31 +5034,31 @@
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -3552,67 +5084,67 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>321693</t>
+          <t>314018</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -3623,42 +5155,52 @@
         </is>
       </c>
       <c r="V4" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
         <v>3</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
@@ -3671,88 +5213,814 @@
         </is>
       </c>
       <c r="AN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="AV4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
         <v>2</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD4" t="n">
         <v>2</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>321694</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>70.8%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>10</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>321693</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" t="n">
+        <v>28</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>59.1%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>64.7%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>77.3%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>7</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="BG4" t="n">
+      <c r="BC6" t="n">
         <v>2</v>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
         <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SLB_A._DZIEWA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>313937</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +6077,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -3953,27 +6221,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -3983,7 +6251,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4032,41 +6300,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -4077,7 +6345,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -4085,7 +6353,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -4093,7 +6361,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -4115,41 +6383,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>16</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6</v>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -4160,7 +6428,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -4168,7 +6436,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -4176,7 +6444,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -4198,31 +6466,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -4232,7 +6500,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -4243,7 +6511,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -4251,7 +6519,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -4259,7 +6527,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -4285,7 +6553,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -4295,11 +6563,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -4308,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -4326,7 +6594,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -4334,7 +6602,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -4362,21 +6630,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -4385,14 +6653,14 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -4403,7 +6671,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -4411,7 +6679,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -4439,7 +6707,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -4583,27 +6851,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -4613,7 +6881,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4666,13 +6934,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4683,10 +6951,10 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -4696,14 +6964,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -4711,7 +6979,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -4719,7 +6987,7 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -4749,21 +7017,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.125</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4772,21 +7040,21 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -4794,7 +7062,7 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -4802,7 +7070,7 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -4832,27 +7100,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28</v>
+      </c>
+      <c r="K5" t="n">
         <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>11.8%</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -4862,14 +7130,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -4877,15 +7145,15 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -4904,7 +7172,1345 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="29" customWidth="1" min="22" max="22"/>
+    <col width="38" customWidth="1" min="23" max="23"/>
+    <col width="35" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>team_key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>global_player_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fg2a</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg2m</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>eligible_zone_profile</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume_all</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct_all</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume_qualified</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct_qualified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>321694</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>321695</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>321693</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>272930</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>321693</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>321695</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>28.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>272930</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>321694</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SLB_A._DZIEWA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>313937</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>272930</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>321694</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>314018</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4913,7 +8519,7 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -5073,46 +8679,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>321694</t>
+          <t>321695</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" t="n">
         <v>7</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -5122,7 +8728,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -5133,7 +8739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -5141,7 +8747,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -5149,7 +8755,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5171,46 +8777,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>321695</t>
+          <t>321694</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -5231,7 +8837,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -5239,7 +8845,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -5247,136 +8853,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SL Benfica</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SLB_L._MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>321694</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>L. Muhammad</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
           <t>300.0%</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sem dados</t>
         </is>
       </c>
     </row>
